--- a/Stage2_Top50_Global_LATEST.xlsx
+++ b/Stage2_Top50_Global_LATEST.xlsx
@@ -20,7 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concall Summaries" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business 1-Pager" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward Valuation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WoW Diff" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thesis Tracker" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WoW Diff" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,29 +145,34 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E8E3E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B26800"/>
+      <color rgb="001F2A44"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <color rgb="00111111"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -188,8 +194,23 @@
         <fgColor rgb="00F7F4EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8E3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C5A572"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D93025"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -211,11 +232,25 @@
         <color rgb="00D9D2C2"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -302,26 +337,34 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12161,7 +12204,3444 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F75"/>
+  <dimension ref="B1:N55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>Thesis Tracker - conviction + scorecard over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>As of 2026-06-06 | 50 in-screen, 50 tracked | Persistent: names leaving the Top 50 keep history (dormant) | Conviction = momentum-led with valuation haircut | weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C5" s="39" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>Conviction</t>
+        </is>
+      </c>
+      <c r="F5" s="39" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
+        <is>
+          <t>Wks</t>
+        </is>
+      </c>
+      <c r="H5" s="39" t="inlineStr">
+        <is>
+          <t>Thesis statement</t>
+        </is>
+      </c>
+      <c r="I5" s="39" t="inlineStr">
+        <is>
+          <t>Pillars (bull case)</t>
+        </is>
+      </c>
+      <c r="J5" s="39" t="inlineStr">
+        <is>
+          <t>Falsifier (wrong if...)</t>
+        </is>
+      </c>
+      <c r="K5" s="39" t="inlineStr">
+        <is>
+          <t>Base target</t>
+        </is>
+      </c>
+      <c r="L5" s="39" t="inlineStr">
+        <is>
+          <t>Bull target</t>
+        </is>
+      </c>
+      <c r="M5" s="39" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+      <c r="N5" s="39" t="inlineStr">
+        <is>
+          <t>Latest data point</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="B6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>RPI.L</t>
+        </is>
+      </c>
+      <c r="D6" s="40" t="inlineStr">
+        <is>
+          <t>Raspberry Pi Holdings plc</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>RPI pre-announced a strong H1 FY26 with adjusted EBITDA of at least $38m and flagged full-year EBITDA 'significantly ahead' of the ~$42m consensus, sending shares sharply higher.</t>
+        </is>
+      </c>
+      <c r="I6" s="42" t="inlineStr">
+        <is>
+          <t>- FY26 EBITDA guided 'significantly ahead' of $42m consensus
+- In-house RP2040/RP2350 silicon now outshipping boards, lifting margins
+- H1 unit volumes above 4m, structural embedded/industrial demand growth</t>
+        </is>
+      </c>
+      <c r="J6" s="42" t="inlineStr">
+        <is>
+          <t>Management flagged H2 unit economics will moderate as cheap memory depletes</t>
+        </is>
+      </c>
+      <c r="K6" s="42" t="inlineStr">
+        <is>
+          <t>679.9 (-35%)</t>
+        </is>
+      </c>
+      <c r="L6" s="42" t="inlineStr">
+        <is>
+          <t>1233.5 (+17%)</t>
+        </is>
+      </c>
+      <c r="M6" s="42" t="inlineStr">
+        <is>
+          <t>- H1 FY26 interim results (Sept 2026)
+- Memory contract pricing trajectory into H2
+- New compute module / silicon product launches</t>
+        </is>
+      </c>
+      <c r="N6" s="42" t="inlineStr">
+        <is>
+          <t>Raspberry Pi pre-announced a strong H1 with adjusted EBITDA of at least $38m and flagged FY26 EBITDA materially ahead of the $42m consensus, lifted by cheap legacy DRAM inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="B7" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Sandisk Corporation</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="44" t="inlineStr">
+        <is>
+          <t>Sandisk's post-spinoff identity as a pure-play NAND/SSD operator is paying off as enterprise SSD pricing rises sharply and HDD-to-SSD substitution accelerates in data centers.</t>
+        </is>
+      </c>
+      <c r="I7" s="44" t="inlineStr">
+        <is>
+          <t>- Hyperscaler NAND allocations rising as AI capex expands
+- Industry capex restrained — Samsung/Hynix prioritizing HBM
+- BiCS8 process node hits enterprise QLC sweet spot</t>
+        </is>
+      </c>
+      <c r="J7" s="44" t="inlineStr">
+        <is>
+          <t>NAND is most cyclical memory segment — single hyperscaler pause hits hard</t>
+        </is>
+      </c>
+      <c r="K7" s="44" t="inlineStr">
+        <is>
+          <t>1691.6 (+8%)</t>
+        </is>
+      </c>
+      <c r="L7" s="44" t="inlineStr">
+        <is>
+          <t>3472.1 (+123%)</t>
+        </is>
+      </c>
+      <c r="M7" s="44" t="inlineStr">
+        <is>
+          <t>- Q1 2026 earnings — pricing trajectory commentary
+- Samsung HBM3E qualification timing at NVIDIA
+- Hyperscaler capex guidance updates Q4-Q1</t>
+        </is>
+      </c>
+      <c r="N7" s="44" t="inlineStr">
+        <is>
+          <t>Sandisk delivered a NAND-supercycle blowout - Q3 revenue of $5.95B (+251% YoY, +97% sequentially) with 78.4% GM, and locked in a $42B multi-year revenue backlog underpinned by $11B of enforceable hyperscaler guarantees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="B8" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="inlineStr">
+        <is>
+          <t>DigitalOcean Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="42" t="inlineStr">
+        <is>
+          <t>DigitalOcean is breaking out as small/mid-market AI adoption finally inflects — its GPU droplet product is fully booked and margin profile is recovering after 18 months of compressed gross margins from AI capex.</t>
+        </is>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
+        <is>
+          <t>- GPU droplet fully booked — pricing power demonstrated
+- Operating margin expansion from AI capex absorption ending
+- SMB AI adoption inflecting — TAM expanding faster than guided</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
+        <is>
+          <t>Competing vs trillion-dollar hyperscalers on price</t>
+        </is>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t>148.2 (-13%)</t>
+        </is>
+      </c>
+      <c r="L8" s="42" t="inlineStr">
+        <is>
+          <t>232.2 (+37%)</t>
+        </is>
+      </c>
+      <c r="M8" s="42" t="inlineStr">
+        <is>
+          <t>- Q1 2026 earnings — net new ARR commentary
+- Vector DB + managed inference adoption metrics
+- NVIDIA H200 supply normalization timing</t>
+        </is>
+      </c>
+      <c r="N8" s="42" t="inlineStr">
+        <is>
+          <t>DigitalOcean's AI bet is paying off - Q1 revenue of $258M (+22% YoY) blew past consensus, AI ARR up 221% to $170M, and mgmt raised 2026 growth guide while flagging 50%+ growth for 2027 on the new AI-Native Cloud launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="B9" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>STMPA.PA</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>STMicroelectronics N.V.</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>STMicroelectronics is breaking out as European auto-semi pricing inflects and the company's silicon-carbide (SiC) MOSFET wafer ramp at Catania crosses commercial scale.</t>
+        </is>
+      </c>
+      <c r="I9" s="44" t="inlineStr">
+        <is>
+          <t>- SiC MOSFET wafer ramp at Catania crosses commercial scale in 2026
+- Chinese EV OEM design wins create multi-year revenue visibility
+- Net cash position funds aggressive buybacks vs leveraged peers</t>
+        </is>
+      </c>
+      <c r="J9" s="44" t="inlineStr">
+        <is>
+          <t>SiC pricing pressure from TankeBlue/SICC compresses gross margins</t>
+        </is>
+      </c>
+      <c r="K9" s="44" t="inlineStr">
+        <is>
+          <t>85.2 (+36%)</t>
+        </is>
+      </c>
+      <c r="L9" s="44" t="inlineStr">
+        <is>
+          <t>155.8 (+148%)</t>
+        </is>
+      </c>
+      <c r="M9" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Jan 2026) — Catania ramp commentary
+- Investor Day March 2026 — 2026 revenue guidance update
+- Apple supplier disclosure cycle (May 2026)</t>
+        </is>
+      </c>
+      <c r="N9" s="44" t="inlineStr">
+        <is>
+          <t>Revenue beat at $3.1B with Q2 guide of $3.45B signaling cyclical bottom is behind ST, but Q1 EPS missed at $0.13 vs $0.17 consensus on restructuring drag and unused capacity charges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="B10" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>Arm Holdings plc</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="42" t="inlineStr">
+        <is>
+          <t>Arm closed FY26 with record Q4 revenue of $1.49bn (+20% YoY) on surging Armv9/CSS royalty rates and data-center adoption, and disclosed its AGI-chip demand book has doubled to over $2bn across the nex</t>
+        </is>
+      </c>
+      <c r="I10" s="42" t="inlineStr">
+        <is>
+          <t>- Record Q4 revenue +20% YoY on Armv9/CSS royalty-rate expansion
+- AGI chip demand doubled to &gt;$2bn over two years
+- Data-center royalty revenue more than doubling YoY</t>
+        </is>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
+        <is>
+          <t>Premium valuation leaves no room for royalty deceleration</t>
+        </is>
+      </c>
+      <c r="K10" s="42" t="inlineStr">
+        <is>
+          <t>247.4 (-28%)</t>
+        </is>
+      </c>
+      <c r="L10" s="42" t="inlineStr">
+        <is>
+          <t>500.0 (+46%)</t>
+        </is>
+      </c>
+      <c r="M10" s="42" t="inlineStr">
+        <is>
+          <t>- Q1 FY27 earnings
+- AGI chip order-book updates
+- Hyperscaler custom-silicon design-win announcements</t>
+        </is>
+      </c>
+      <c r="N10" s="42" t="inlineStr">
+        <is>
+          <t>Arm closed FY26 with record Q4 revenue of $1.49bn (up 20% YoY) on surging Armv9/CSS royalty rates and data-center adoption, and disclosed AGI-chip demand has doubled to over $2bn across the next two years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="B11" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Marvell Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="44" t="inlineStr">
+        <is>
+          <t>Marvell posted record Q1 FY27 revenue of $2.418bn (+28% YoY) and pulled forward its $3bn quarterly run-rate to Q3, guiding data center to grow ~50% in FY27 on custom silicon and an expanded NVIDIA par</t>
+        </is>
+      </c>
+      <c r="I11" s="44" t="inlineStr">
+        <is>
+          <t>- $3bn quarterly run-rate pulled forward to Q3 FY27
+- Data center guided ~50% FY27 growth on custom silicon
+- Interconnect business &gt;70% YoY growth</t>
+        </is>
+      </c>
+      <c r="J11" s="44" t="inlineStr">
+        <is>
+          <t>Hyperscaler customer/program concentration risk</t>
+        </is>
+      </c>
+      <c r="K11" s="44" t="inlineStr">
+        <is>
+          <t>185.0 (-30%)</t>
+        </is>
+      </c>
+      <c r="L11" s="44" t="inlineStr">
+        <is>
+          <t>302.9 (+15%)</t>
+        </is>
+      </c>
+      <c r="M11" s="44" t="inlineStr">
+        <is>
+          <t>- Q2 FY27 earnings
+- New custom-silicon program wins
+- Optical/interconnect attach-rate updates</t>
+        </is>
+      </c>
+      <c r="N11" s="44" t="inlineStr">
+        <is>
+          <t>Marvell posted record Q1 FY27 revenue of $2.418bn (+28% YoY) and pulled forward its $3bn quarterly run-rate to Q3, with data center set to grow ~50% in FY27 on custom silicon and an expanded NVIDIA partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="B12" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>Micron Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="42" t="inlineStr">
+        <is>
+          <t>Micron is breaking back to highs as HBM3E and HBM4 ramp ahead of plan, and DRAM contract prices for 2026 have already been locked higher than sell-side models assumed.</t>
+        </is>
+      </c>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>- HBM3E ramp ahead of plan; HBM4 design wins locked
+- DRAM contract prices for 2026 above sell-side models
+- Industry supply discipline structural this cycle</t>
+        </is>
+      </c>
+      <c r="J12" s="42" t="inlineStr">
+        <is>
+          <t>Memory cycles deeply cyclical — hyperscaler pause hits 2H</t>
+        </is>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>1126.7 (+30%)</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>2480.7 (+187%)</t>
+        </is>
+      </c>
+      <c r="M12" s="42" t="inlineStr">
+        <is>
+          <t>- Q2 FY26 earnings (March 2026) — pricing + HBM mix
+- NVIDIA Blackwell Ultra launch timing
+- Samsung HBM3E qualification announcement</t>
+        </is>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Micron beat on record fiscal Q2 revenue and guided fiscal Q3 to $18.7bn with ~68% gross margin, raising FY26 capex to $20bn as it locks in all 2026 HBM pricing and pulls its $100bn HBM TAM forecast forward two years to 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="B13" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Dell Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>Dell is breaking out as AI server backlog reaches record levels and ISG (Infrastructure Solutions) margin expansion finally arrives.</t>
+        </is>
+      </c>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>- AI server backlog at record levels, broadening beyond xAI
+- ISG margin expansion finally arriving
+- Capital return &gt;4% yield (dividend + buyback)</t>
+        </is>
+      </c>
+      <c r="J13" s="44" t="inlineStr">
+        <is>
+          <t>AI server gross margins structurally lower than legacy ISG</t>
+        </is>
+      </c>
+      <c r="K13" s="44" t="inlineStr">
+        <is>
+          <t>687.3 (+74%)</t>
+        </is>
+      </c>
+      <c r="L13" s="44" t="inlineStr">
+        <is>
+          <t>1231.7 (+212%)</t>
+        </is>
+      </c>
+      <c r="M13" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 FY26 earnings (Feb 2026) — backlog + margin commentary
+- NVIDIA GB200/B300 GA timing
+- CES 2026 AI-PC product launches</t>
+        </is>
+      </c>
+      <c r="N13" s="44" t="inlineStr">
+        <is>
+          <t>Dell blew out Q1 FY27 with record $43.8B revenue (+88% YoY) on $24.4B of AI server orders, raising FY27 revenue guide to ~$167B and signaling demand exceeds supply across DRAM, NAND and CPUs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="B14" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>Infineon Technologies AG</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="42" t="inlineStr">
+        <is>
+          <t>Infineon raised FY26 guidance to over EUR 16bn revenue and ~20% segment margin as AI-related power revenue nearly tripled YoY and automotive order intake began recovering.</t>
+        </is>
+      </c>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>- FY26 guidance raised to &gt;EUR 16bn revenue, ~20% margin
+- AI power revenue nearly tripled YoY; EUR 2.5bn FY27 target
+- Automotive order intake inflecting positive</t>
+        </is>
+      </c>
+      <c r="J14" s="42" t="inlineStr">
+        <is>
+          <t>High-voltage e-mobility still weak</t>
+        </is>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>95.1 (+23%)</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>172.8 (+123%)</t>
+        </is>
+      </c>
+      <c r="M14" s="42" t="inlineStr">
+        <is>
+          <t>- Q3 FY26 earnings
+- AI power revenue ramp updates
+- Automotive order-intake trajectory</t>
+        </is>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Infineon raised FY26 guidance to over EUR 16bn revenue and ~20% segment margin as AI-related revenue nearly tripled YoY and automotive order intake began recovering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="B15" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Astera Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="E15" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G15" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>Astera delivered Q1 2026 revenue of $308.4m (+93% YoY) and guided Q2 to $355-365m (+15-18% QoQ), with growth broadening across signal conditioning and switch fabric as Scorpio and PCIe 6.0 ramp.</t>
+        </is>
+      </c>
+      <c r="I15" s="44" t="inlineStr">
+        <is>
+          <t>- Q1 revenue +93% YoY, Q2 guided +15-18% QoQ
+- Scorpio switch fabric diversifying beyond retimers
+- PCIe 6.0 traction across AI fabric</t>
+        </is>
+      </c>
+      <c r="J15" s="44" t="inlineStr">
+        <is>
+          <t>Very high valuation tied to AI-capex sentiment</t>
+        </is>
+      </c>
+      <c r="K15" s="44" t="inlineStr">
+        <is>
+          <t>183.4 (-42%)</t>
+        </is>
+      </c>
+      <c r="L15" s="44" t="inlineStr">
+        <is>
+          <t>246.4 (-22%)</t>
+        </is>
+      </c>
+      <c r="M15" s="44" t="inlineStr">
+        <is>
+          <t>- Q2 2026 earnings
+- Scorpio switch ramp milestones
+- New hyperscaler design wins</t>
+        </is>
+      </c>
+      <c r="N15" s="44" t="inlineStr">
+        <is>
+          <t>Astera Labs delivered Q1 revenue of $308.4m (+93% YoY) and guided Q2 to $355-365m (+15-18% QoQ), with growth broadening across signal conditioning and switch fabric as Scorpio and PCIe 6.0 ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="B16" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>Flex Ltd.</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="42" t="inlineStr">
+        <is>
+          <t>Flex (EMS) is breaking out as Nextracker spin/sell value crystallizes and the core EMS business pivots into higher-margin AI/data-center power and liquid-cooling sub-systems.</t>
+        </is>
+      </c>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>- Nextracker monetization cleaned cap structure
+- Liquid-cooling CDU + busbar wins at 2 of 4 hyperscalers
+- Order book visibility rarely this clean</t>
+        </is>
+      </c>
+      <c r="J16" s="42" t="inlineStr">
+        <is>
+          <t>EMS structurally low-margin</t>
+        </is>
+      </c>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>208.1 (+37%)</t>
+        </is>
+      </c>
+      <c r="L16" s="42" t="inlineStr">
+        <is>
+          <t>358.2 (+136%)</t>
+        </is>
+      </c>
+      <c r="M16" s="42" t="inlineStr">
+        <is>
+          <t>- Q3 FY26 earnings (Jan 2026) — power/cooling mix
+- Hyperscaler liquid cooling rollout disclosures
+- Nextracker IPO performance</t>
+        </is>
+      </c>
+      <c r="N16" s="42" t="inlineStr">
+        <is>
+          <t>Flex announced a planned spin-off of its Cloud &amp; Power Infrastructure segment (targeted 1Q calendar 2027), unmasking a 65-75% growth SpinCo and leaving RemainCo as a slower, healthcare/automation story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="B17" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="E17" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G17" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>Intel beat for a sixth straight quarter with Q1 2026 revenue of $13.6bn ($1.4bn above midpoint) and a narrowing foundry loss, but warned H2 gross margins face headwinds from the early 18A ramp and ris</t>
+        </is>
+      </c>
+      <c r="I17" s="44" t="inlineStr">
+        <is>
+          <t>- Sixth straight quarterly beat; Q1 $1.4bn above midpoint
+- Foundry loss narrowing, revenue +20% sequential
+- 18A yields ahead of internal projections</t>
+        </is>
+      </c>
+      <c r="J17" s="44" t="inlineStr">
+        <is>
+          <t>18A ramp dilutes near-term gross margin</t>
+        </is>
+      </c>
+      <c r="K17" s="44" t="inlineStr">
+        <is>
+          <t>85.4 (-14%)</t>
+        </is>
+      </c>
+      <c r="L17" s="44" t="inlineStr">
+        <is>
+          <t>160.1 (+61%)</t>
+        </is>
+      </c>
+      <c r="M17" s="44" t="inlineStr">
+        <is>
+          <t>- Q2 2026 earnings
+- 18A volume-ramp and yield updates
+- External foundry customer announcements</t>
+        </is>
+      </c>
+      <c r="N17" s="44" t="inlineStr">
+        <is>
+          <t>Intel beat for a sixth straight quarter with Q1 revenue of $13.6bn ($1.4bn above midpoint) and a narrowing foundry loss, but warned H2 gross margins face headwinds from the early 18A ramp and rising memory input costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="B18" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>Seagate Technology Holdings pl</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="42" t="inlineStr">
+        <is>
+          <t>Seagate is breaking out as nearline HDD pricing rises for the fifth consecutive quarter — exabytes shipped to hyperscalers are growing and HAMR (heat-assisted magnetic recording) drives are now in vol</t>
+        </is>
+      </c>
+      <c r="I18" s="42" t="inlineStr">
+        <is>
+          <t>- Nearline HDD pricing up five quarters running
+- HAMR drives at 30+ TB density restore cost/TB vs SSD for cold storage
+- AI training data exhaust = HDD demand secular</t>
+        </is>
+      </c>
+      <c r="J18" s="42" t="inlineStr">
+        <is>
+          <t>QLC NAND pricing collapse re-opens HDD substitution</t>
+        </is>
+      </c>
+      <c r="K18" s="42" t="inlineStr">
+        <is>
+          <t>786.0 (-7%)</t>
+        </is>
+      </c>
+      <c r="L18" s="42" t="inlineStr">
+        <is>
+          <t>1305.9 (+54%)</t>
+        </is>
+      </c>
+      <c r="M18" s="42" t="inlineStr">
+        <is>
+          <t>- Q3 FY26 earnings (Jan 2026) — HAMR exabyte mix
+- Hyperscaler 2026 capex commentary
+- WDC HAMR catch-up timing</t>
+        </is>
+      </c>
+      <c r="N18" s="42" t="inlineStr">
+        <is>
+          <t>Seagate posted a blowout HAMR-driven Q3 with revenue of $3.11B (+44% YoY), non-GAAP EPS of $4.10, and ~$1B FCF - with Q4 guide near $3.45B / ~$5.00 EPS and two of the largest CSPs now qualified on Mozaic 4+ HAMR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="96" customHeight="1">
+      <c r="B19" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>STRL</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Sterling Infrastructure, Inc.</t>
+        </is>
+      </c>
+      <c r="E19" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>Sterling Infrastructure is breaking out as data-center site preparation backlog reaches record levels and the company's e-infrastructure segment becomes the dominant profit pool.</t>
+        </is>
+      </c>
+      <c r="I19" s="44" t="inlineStr">
+        <is>
+          <t>- Data-center site preparation backlog at record levels
+- Hyperscaler campus pipeline years deep (TX/AZ/VA)
+- E-infrastructure segment dominant profit pool</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="inlineStr">
+        <is>
+          <t>Fixed-price contracting — cost inflation erodes locked margins</t>
+        </is>
+      </c>
+      <c r="K19" s="44" t="inlineStr">
+        <is>
+          <t>742.0 (-16%)</t>
+        </is>
+      </c>
+      <c r="L19" s="44" t="inlineStr">
+        <is>
+          <t>853.6 (-3%)</t>
+        </is>
+      </c>
+      <c r="M19" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (March 2026) — backlog disclosure
+- Major hyperscaler campus groundbreaking announcements
+- Texas data-center grid interconnect milestones</t>
+        </is>
+      </c>
+      <c r="N19" s="44" t="inlineStr">
+        <is>
+          <t>Revenue +92% and EPS +120% YoY, with mission-critical (data center, semi, manufacturing) now &gt;90% of E-Infrastructure backlog, and management raised full-year guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="96" customHeight="1">
+      <c r="B20" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="42" t="inlineStr">
+        <is>
+          <t>AMD is breaking out as the MI350/MI400 GPU roadmap regains credibility — large hyperscaler wins (Oracle, Meta) are now flowing into the order book, and the gap to NVIDIA's CUDA ecosystem is narrowing as ROCm matures.</t>
+        </is>
+      </c>
+      <c r="I20" s="42" t="inlineStr">
+        <is>
+          <t>- MI350/MI400 GPU roadmap regaining credibility — Oracle, Meta wins
+- EPYC server CPU share above 30% in cloud — sticky high margin
+- Xilinx integration finally paying off in embedded/auto</t>
+        </is>
+      </c>
+      <c r="J20" s="42" t="inlineStr">
+        <is>
+          <t>NVIDIA Rubin/Blackwell Ultra raises bar relentlessly</t>
+        </is>
+      </c>
+      <c r="K20" s="42" t="inlineStr">
+        <is>
+          <t>358.7 (-23%)</t>
+        </is>
+      </c>
+      <c r="L20" s="42" t="inlineStr">
+        <is>
+          <t>573.4 (+23%)</t>
+        </is>
+      </c>
+      <c r="M20" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (early Feb 2026) — MI350 ramp + data-center segment
+- Computex / GTC keynote calendar
+- Hyperscaler capex guidance for 2026</t>
+        </is>
+      </c>
+      <c r="N20" s="42" t="inlineStr">
+        <is>
+          <t>AMD beat across the board with Q1 revenue of $10.3B (+38% YoY) led by 57% Data Center growth, and Lisa Su laid out a path to &gt;$20 EPS over the strategic horizon as MI350 ramps into hyperscaler pods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="96" customHeight="1">
+      <c r="B21" s="43" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>Ciena Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G21" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>Ciena is breaking out as cloud DCI (data-center interconnect) orders accelerate with hyperscaler east-west bandwidth needs and the company's WaveLogic 6 optical engine wins the next-gen 800ZR+ socket</t>
+        </is>
+      </c>
+      <c r="I21" s="44" t="inlineStr">
+        <is>
+          <t>- WaveLogic 6 wins next-gen 800ZR+ socket at webscale customers
+- Cloud DCI orders accelerating with AI east-west bandwidth
+- Service-provider business stabilizing</t>
+        </is>
+      </c>
+      <c r="J21" s="44" t="inlineStr">
+        <is>
+          <t>Cisco + Acacia + Nokia create real price pressure</t>
+        </is>
+      </c>
+      <c r="K21" s="44" t="inlineStr">
+        <is>
+          <t>360.0 (-26%)</t>
+        </is>
+      </c>
+      <c r="L21" s="44" t="inlineStr">
+        <is>
+          <t>561.7 (+15%)</t>
+        </is>
+      </c>
+      <c r="M21" s="44" t="inlineStr">
+        <is>
+          <t>- Q1 FY26 earnings (March 2026) — DCI bookings
+- Cisco Acacia roadmap updates
+- Major hyperscaler optical refresh wins</t>
+        </is>
+      </c>
+      <c r="N21" s="44" t="inlineStr">
+        <is>
+          <t>Ciena posted fiscal Q2 revenue of $1.57bn (+40% YoY) with adjusted EPS up 290%, and raised FY26 revenue guidance to $6.3bn as AI-driven data-center interconnect, including its first multi-rail Hyper-Rail win, accelerates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1">
+      <c r="B22" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>Western Digital Corporation</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="42" t="inlineStr">
+        <is>
+          <t>Western Digital is breaking out post-NAND separation (which became Sandisk) — pure-play HDD operator with HAMR drives ramping and pricing rising.</t>
+        </is>
+      </c>
+      <c r="I22" s="42" t="inlineStr">
+        <is>
+          <t>- Pure-play HDD post-NAND-spinoff — cleaner story
+- Same AI cold-storage tailwind as STX
+- Post-separation balance sheet cleaner than expected</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>Trails STX on HAMR rollout — execution risk</t>
+        </is>
+      </c>
+      <c r="K22" s="42" t="inlineStr">
+        <is>
+          <t>529.6 (+4%)</t>
+        </is>
+      </c>
+      <c r="L22" s="42" t="inlineStr">
+        <is>
+          <t>885.1 (+73%)</t>
+        </is>
+      </c>
+      <c r="M22" s="42" t="inlineStr">
+        <is>
+          <t>- Q2 FY26 earnings (Jan 2026) — HAMR ramp progress
+- Hyperscaler 2026 storage capex guidance
+- HAMR competitive positioning vs STX</t>
+        </is>
+      </c>
+      <c r="N22" s="42" t="inlineStr">
+        <is>
+          <t>HDD-pure-play WDC printed &gt;50% gross margin and 45% YoY revenue growth, anchoring management's call for a 25%+ cloud exabyte CAGR driven by agentic AI workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="96" customHeight="1">
+      <c r="B23" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>VICR</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Vicor Corporation</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G23" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="44" t="inlineStr">
+        <is>
+          <t>Vicor is breaking out as its second-generation factorized power architecture wins design slots in next-generation AI accelerator boards — power density per rack-unit is the binding constraint for NVID</t>
+        </is>
+      </c>
+      <c r="I23" s="44" t="inlineStr">
+        <is>
+          <t>- 48V-to-PoL conversion essential for NVIDIA Blackwell+ servers
+- Andover automotive fab yields improving
+- Operating leverage significant on fixed-cost base</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="inlineStr">
+        <is>
+          <t>'Next year' story for half a decade — execution risk</t>
+        </is>
+      </c>
+      <c r="K23" s="44" t="inlineStr">
+        <is>
+          <t>242.2 (-11%)</t>
+        </is>
+      </c>
+      <c r="L23" s="44" t="inlineStr">
+        <is>
+          <t>328.9 (+21%)</t>
+        </is>
+      </c>
+      <c r="M23" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — revenue ramp signal
+- NVIDIA Blackwell power architecture disclosures
+- Major automotive design-win announcements</t>
+        </is>
+      </c>
+      <c r="N23" s="44" t="inlineStr">
+        <is>
+          <t>Record Q1 with backlog up 70% QoQ to $300.6M validates the AI/HPC power thesis, but full-year guide stays conservative pending second ITC ruling in 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="96" customHeight="1">
+      <c r="B24" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Com</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="42" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise is breaking out as Cray-AI supercomputer orders accelerate from sovereign/hyperscale customers and the Juniper Networks acquisition closes (regulatory hurdle removed).</t>
+        </is>
+      </c>
+      <c r="I24" s="42" t="inlineStr">
+        <is>
+          <t>- Cray-AI supercomputer orders accelerating (sovereign + hyperscale)
+- Juniper acquisition closes — networking attach expansion
+- AI server backlog at record levels</t>
+        </is>
+      </c>
+      <c r="J24" s="42" t="inlineStr">
+        <is>
+          <t>Same hyperscaler-concentration risk as Dell</t>
+        </is>
+      </c>
+      <c r="K24" s="42" t="inlineStr">
+        <is>
+          <t>60.8 (+24%)</t>
+        </is>
+      </c>
+      <c r="L24" s="42" t="inlineStr">
+        <is>
+          <t>80.0 (+63%)</t>
+        </is>
+      </c>
+      <c r="M24" s="42" t="inlineStr">
+        <is>
+          <t>- Q1 FY26 earnings (March 2026) — backlog + Juniper integration
+- NVIDIA platform launches
+- Major sovereign AI awards</t>
+        </is>
+      </c>
+      <c r="N24" s="42" t="inlineStr">
+        <is>
+          <t>HPE beat with Q2 revenue of $10.7bn above the high end of guidance and raised FY26 EPS to $3.40 at the midpoint, as AI systems orders hit $1.8bn and the Juniper integration tracked ahead of synergy milestones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1">
+      <c r="B25" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>TEM.L</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>Templeton Emerging Markets Inv</t>
+        </is>
+      </c>
+      <c r="E25" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G25" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>TEM.L is breaking out alongside a broad emerging-market equity recovery and a narrowing discount to NAV.</t>
+        </is>
+      </c>
+      <c r="I25" s="44" t="inlineStr">
+        <is>
+          <t>- EM equity recovery on softer dollar backdrop
+- Discount-to-NAV narrowing adds to price return
+- Attractive relative valuation vs US mega-cap</t>
+        </is>
+      </c>
+      <c r="J25" s="44" t="inlineStr">
+        <is>
+          <t>No business moat - pure market beta</t>
+        </is>
+      </c>
+      <c r="K25" s="44" t="inlineStr"/>
+      <c r="L25" s="44" t="inlineStr"/>
+      <c r="M25" s="44" t="inlineStr">
+        <is>
+          <t>- Monthly NAV/portfolio updates
+- EM index direction and USD trajectory
+- Discount-management/buyback actions</t>
+        </is>
+      </c>
+      <c r="N25" s="44" t="inlineStr">
+        <is>
+          <t>Vehicle does not issue quarterly earnings (Templeton Emerging Markets Investment Trust, closed-end fund) - see NAV updates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="B26" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D26" s="40" t="inlineStr">
+        <is>
+          <t>ON Semiconductor Corporation</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="42" t="inlineStr">
+        <is>
+          <t>ON Semiconductor is breaking out as the auto SiC inventory correction ends and the company's intelligent power and sensing portfolio sees strong design-win momentum from Chinese EV OEMs and European Tier-1s.</t>
+        </is>
+      </c>
+      <c r="I26" s="42" t="inlineStr">
+        <is>
+          <t>- Auto SiC inventory correction ending — design-win momentum strong
+- Chinese EV + European Tier-1 wins flowing through
+- Tower acquisition synergies in P&amp;L</t>
+        </is>
+      </c>
+      <c r="J26" s="42" t="inlineStr">
+        <is>
+          <t>Auto OEM build-rate volatility hits ON faster than peers</t>
+        </is>
+      </c>
+      <c r="K26" s="42" t="inlineStr">
+        <is>
+          <t>157.9 (+35%)</t>
+        </is>
+      </c>
+      <c r="L26" s="42" t="inlineStr">
+        <is>
+          <t>287.3 (+145%)</t>
+        </is>
+      </c>
+      <c r="M26" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — SiC backlog + auto inventory
+- Tier-1 customer SiC announcements
+- Tower fab consolidation milestones</t>
+        </is>
+      </c>
+      <c r="N26" s="42" t="inlineStr">
+        <is>
+          <t>ON beat Q1 with $1.51B revenue and $0.64 EPS, guided Q2 +7% sequentially, and reiterated AI data-center revenue will double YoY in 2026 led by 55% SiC share in new China EV models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="96" customHeight="1">
+      <c r="B27" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>OGN</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Organon &amp; Co.</t>
+        </is>
+      </c>
+      <c r="E27" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G27" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>Organon agreed to be acquired by Sun Pharma for $14.00/share all-cash (~$11.75bn EV).</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr">
+        <is>
+          <t>- Definitive $14.00/share all-cash Sun Pharma deal
+- Q1 adjusted EBITDA $415m supports valuation
+- Limited fundamental downside given cash floor</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>Upside capped at deal price</t>
+        </is>
+      </c>
+      <c r="K27" s="44" t="inlineStr">
+        <is>
+          <t>15.9 (+19%)</t>
+        </is>
+      </c>
+      <c r="L27" s="44" t="inlineStr">
+        <is>
+          <t>21.7 (+62%)</t>
+        </is>
+      </c>
+      <c r="M27" s="44" t="inlineStr">
+        <is>
+          <t>- Merger proxy / shareholder vote
+- Antitrust clearances
+- Expected close timing</t>
+        </is>
+      </c>
+      <c r="N27" s="44" t="inlineStr">
+        <is>
+          <t>Organon suspended its earnings call after agreeing to be acquired by Sun Pharma for $14.00/share all-cash ($11.75B EV); Q1 print was solid but the deal is the whole story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="96" customHeight="1">
+      <c r="B28" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>SITM</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>SiTime Corporation</t>
+        </is>
+      </c>
+      <c r="E28" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="42" t="inlineStr">
+        <is>
+          <t>SiTime is breaking out as its MEMS-based precision timing solutions become standard content on every NVIDIA Blackwell/Rubin AI server, pushing Q1 2026 revenue +88% YoY to $113.6M and prompting a guide</t>
+        </is>
+      </c>
+      <c r="I28" s="42" t="inlineStr">
+        <is>
+          <t>- AI server $-content per box continues stepping up with each NVIDIA platform
+- FY26 growth guide of &gt;=80% with order book visibility extending multi-quarters
+- GM expansion to mid-60s% on AI/networking mix</t>
+        </is>
+      </c>
+      <c r="J28" s="42" t="inlineStr">
+        <is>
+          <t>Customer concentration risk - lead hyperscaler still ~50% of growth</t>
+        </is>
+      </c>
+      <c r="K28" s="42" t="inlineStr">
+        <is>
+          <t>560.3 (-10%)</t>
+        </is>
+      </c>
+      <c r="L28" s="42" t="inlineStr">
+        <is>
+          <t>692.5 (+11%)</t>
+        </is>
+      </c>
+      <c r="M28" s="42" t="inlineStr">
+        <is>
+          <t>- Q2 2026 print (guide $1.24 EPS)
+- NVIDIA Rubin launch detail (H2 2026)
+- Hyperscaler capex commentary</t>
+        </is>
+      </c>
+      <c r="N28" s="42" t="inlineStr">
+        <is>
+          <t>SiTime posted a blowout Q1 with revenue +88% YoY to $113.6M as AI/data-center MEMS timing ramps inflect, and management raised full-year revenue growth guide to at least 80%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="96" customHeight="1">
+      <c r="B29" s="43" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>BESI.AS</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>BE Semiconductor Industries N.</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F29" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G29" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>BE Semiconductor (BESI) is breaking out as hybrid-bonding tool orders accelerate — this is the assembly tech that enables HBM4 stacking and advanced 3D packaging.</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr">
+        <is>
+          <t>- Hybrid-bonding monopoly — closest thing to ASML EUV lock-in
+- HBM4 stacking + advanced 3D packaging drives tool intensity
+- TSMC Phoenix + CoWoS expansion unlocks order book</t>
+        </is>
+      </c>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t>TSMC capex push-out moves stock 15%+ per single decision</t>
+        </is>
+      </c>
+      <c r="K29" s="44" t="inlineStr">
+        <is>
+          <t>181.4 (-33%)</t>
+        </is>
+      </c>
+      <c r="L29" s="44" t="inlineStr">
+        <is>
+          <t>291.5 (+7%)</t>
+        </is>
+      </c>
+      <c r="M29" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — 2026 capex guide
+- TSMC capex announcements
+- Samsung packaging tech strategy updates</t>
+        </is>
+      </c>
+      <c r="N29" s="44" t="inlineStr">
+        <is>
+          <t>BESI's hybrid bonding flywheel ignited - Q1 orders surged 105% YoY to 269.7M EUR (above prior 2024 peak) with the hybrid bonding customer base expanding to 20 across logic, memory, photonics and mobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="96" customHeight="1">
+      <c r="B30" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>Coherent Corp.</t>
+        </is>
+      </c>
+      <c r="E30" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="42" t="inlineStr">
+        <is>
+          <t>Coherent is breaking out as datacom transceiver demand (800G, 1.6T) accelerates with hyperscaler GPU cluster builds and the company's vertical integration (in-house InP fabs) becomes a moat as competitors run short on supply.</t>
+        </is>
+      </c>
+      <c r="I30" s="42" t="inlineStr">
+        <is>
+          <t>- 800G/1.6T transceivers supply-constrained through 2026
+- II-VI InP wafer capacity = competitive moat
+- Industrial laser segment stabilizing</t>
+        </is>
+      </c>
+      <c r="J30" s="42" t="inlineStr">
+        <is>
+          <t>Chinese transceiver pricing pressure (Innolight, Eoptolink)</t>
+        </is>
+      </c>
+      <c r="K30" s="42" t="inlineStr">
+        <is>
+          <t>304.9 (-19%)</t>
+        </is>
+      </c>
+      <c r="L30" s="42" t="inlineStr">
+        <is>
+          <t>494.3 (+31%)</t>
+        </is>
+      </c>
+      <c r="M30" s="42" t="inlineStr">
+        <is>
+          <t>- Q2 FY26 earnings (Feb 2026) — networking segment commentary
+- NVIDIA Spectrum-X adoption updates
+- 800G/1.6T adoption rate at hyperscalers</t>
+        </is>
+      </c>
+      <c r="N30" s="42" t="inlineStr">
+        <is>
+          <t>NVIDIA's $2B equity stake plus a multi-year supply agreement reframes Coherent as the optical partner of choice for scale-out and scale-up AI networks through end of decade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="96" customHeight="1">
+      <c r="B31" s="43" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>Affirm Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G31" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>Affirm beat hard on FQ3 2026 (EPS $0.30 vs $0.17, revenue $1.04bn) on Affirm Card momentum and stable credit, but held RLTC guidance at the 4% upper bound rather than raising despite running above tar</t>
+        </is>
+      </c>
+      <c r="I31" s="44" t="inlineStr">
+        <is>
+          <t>- Big FQ3 beat: EPS $0.30 vs $0.17
+- Affirm Card +700k net new cardholders
+- Stable credit, no delinquency increase</t>
+        </is>
+      </c>
+      <c r="J31" s="44" t="inlineStr">
+        <is>
+          <t>Consumer-credit cyclicality / unemployment risk</t>
+        </is>
+      </c>
+      <c r="K31" s="44" t="inlineStr">
+        <is>
+          <t>69.5 (+9%)</t>
+        </is>
+      </c>
+      <c r="L31" s="44" t="inlineStr">
+        <is>
+          <t>81.2 (+28%)</t>
+        </is>
+      </c>
+      <c r="M31" s="44" t="inlineStr">
+        <is>
+          <t>- FQ4 2026 earnings
+- Affirm Card GMV/cardholder updates
+- Credit-performance and funding metrics</t>
+        </is>
+      </c>
+      <c r="N31" s="44" t="inlineStr">
+        <is>
+          <t>Affirm beat hard on FQ3 (EPS $0.30 vs $0.17, revenue $1.04B) on Affirm Card momentum and stable credit, but held RLTC guidance at the 4% upper bound rather than raising despite running above target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="96" customHeight="1">
+      <c r="B32" s="40" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="D32" s="40" t="inlineStr">
+        <is>
+          <t>Iridium Communications Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="42" t="inlineStr">
+        <is>
+          <t>Iridium reaffirmed full-year guidance on modest 2% revenue growth ($218.8m), framing 2026 as a product-launch year (TriMode 9604 modem, PNT ASIC) that sets up the IoT/PNT growth story, even as a comp-</t>
+        </is>
+      </c>
+      <c r="I32" s="42" t="inlineStr">
+        <is>
+          <t>- TriMode 9604 modem and PNT ASIC launching in 2026
+- PNT ASIC drawing 100+ interested companies
+- NTN Direct MNO partnerships add durable demand</t>
+        </is>
+      </c>
+      <c r="J32" s="42" t="inlineStr">
+        <is>
+          <t>Only ~2% revenue growth near term</t>
+        </is>
+      </c>
+      <c r="K32" s="42" t="inlineStr">
+        <is>
+          <t>44.5 (-6%)</t>
+        </is>
+      </c>
+      <c r="L32" s="42" t="inlineStr">
+        <is>
+          <t>56.1 (+18%)</t>
+        </is>
+      </c>
+      <c r="M32" s="42" t="inlineStr">
+        <is>
+          <t>- TriMode 9604 commercial availability
+- PNT ASIC launch and design wins
+- Government program awards</t>
+        </is>
+      </c>
+      <c r="N32" s="42" t="inlineStr">
+        <is>
+          <t>Iridium reaffirmed full-year guidance on modest 2% revenue growth ($218.8M), framing 2026 as a product-launch year (TriMode 9604 modem, PNT ASIC) that sets up the IoT/PNT growth story even as a comp-policy shift dents OIBDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="96" customHeight="1">
+      <c r="B33" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>TTMI</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>TTM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G33" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="44" t="inlineStr">
+        <is>
+          <t>TTM Technologies is breaking out as defense PCB demand surges (multi-year backlog from F-35, Patriot, Aegis upgrade programs) plus commercial AI server PCB orders accelerating.</t>
+        </is>
+      </c>
+      <c r="I33" s="44" t="inlineStr">
+        <is>
+          <t>- Defense PCB backlog &gt;$1B (F-35, Patriot, Aegis programs)
+- Multi-year revenue visibility unusual for segment
+- China divestiture cleaned margin + geopolitical profile</t>
+        </is>
+      </c>
+      <c r="J33" s="44" t="inlineStr">
+        <is>
+          <t>Commercial AI server volume slowdown hits margin mix</t>
+        </is>
+      </c>
+      <c r="K33" s="44" t="inlineStr">
+        <is>
+          <t>184.9 (+10%)</t>
+        </is>
+      </c>
+      <c r="L33" s="44" t="inlineStr">
+        <is>
+          <t>291.1 (+74%)</t>
+        </is>
+      </c>
+      <c r="M33" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — defense backlog + mix
+- FY27 defense budget signals
+- Major AI server platform PCB design wins</t>
+        </is>
+      </c>
+      <c r="N33" s="44" t="inlineStr">
+        <is>
+          <t>Record Q1 with ~80% of sales tied to AI and defense; capex bumped to $310M to accelerate Penang/Syracuse/Wisconsin ramps for AI data-center and aerospace customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="96" customHeight="1">
+      <c r="B34" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>NOD.OL</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="inlineStr">
+        <is>
+          <t>Nordic Semiconductor ASA</t>
+        </is>
+      </c>
+      <c r="E34" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="42" t="inlineStr">
+        <is>
+          <t>Nordic Semiconductor is breaking out on a clear inflection in Bluetooth Low Energy + Wi-Fi 6 chip demand for wearables, hearables, and smart-home, plus first revenue from cellular IoT (nRF91 series).</t>
+        </is>
+      </c>
+      <c r="I34" s="42" t="inlineStr">
+        <is>
+          <t>- Apple Vision Pro 2 + Meta Ray-Ban supply wins shipping volume
+- Cellular IoT (nRF91) moves from pilot to deployment
+- Geopolitical preference for non-Chinese BLE — sticky moat</t>
+        </is>
+      </c>
+      <c r="J34" s="42" t="inlineStr">
+        <is>
+          <t>Wearables consumer-cyclical — weak holiday hits fast</t>
+        </is>
+      </c>
+      <c r="K34" s="42" t="inlineStr">
+        <is>
+          <t>165.2 (-14%)</t>
+        </is>
+      </c>
+      <c r="L34" s="42" t="inlineStr">
+        <is>
+          <t>227.9 (+18%)</t>
+        </is>
+      </c>
+      <c r="M34" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings — wearables ASP trajectory
+- Apple WWDC June 2026 — VR/AR product cycle confirmation
+- Cellular IoT design-win disclosures</t>
+        </is>
+      </c>
+      <c r="N34" s="42" t="inlineStr">
+        <is>
+          <t>Nordic posted a clean beat with Q1 revenue of $192M (+24% YoY) and GM of 52.1%, validating the long-term &gt;20% growth / &gt;50% GM / 25% EBITDA model with new cellular IoT platforms broadening the TAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="96" customHeight="1">
+      <c r="B35" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>PCT.L</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>Polar Capital Technology Trust</t>
+        </is>
+      </c>
+      <c r="E35" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G35" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="44" t="inlineStr">
+        <is>
+          <t>PCT.L is breaking out with the global tech/AI equity rally and a narrowing discount to NAV.</t>
+        </is>
+      </c>
+      <c r="I35" s="44" t="inlineStr">
+        <is>
+          <t>- AI/semis-led global tech rally lifts NAV
+- Discount-to-NAV narrowing adds return
+- Concentrated exposure to AI winners (NVDA)</t>
+        </is>
+      </c>
+      <c r="J35" s="44" t="inlineStr">
+        <is>
+          <t>No moat - pure tech beta</t>
+        </is>
+      </c>
+      <c r="K35" s="44" t="inlineStr"/>
+      <c r="L35" s="44" t="inlineStr"/>
+      <c r="M35" s="44" t="inlineStr">
+        <is>
+          <t>- NAV / interim &amp; final results
+- Nasdaq/semis direction
+- Discount-management actions</t>
+        </is>
+      </c>
+      <c r="N35" s="44" t="inlineStr">
+        <is>
+          <t>Vehicle does not issue quarterly earnings - Polar Capital Technology Trust is a closed-end investment trust; see NAV updates and interim/final results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="96" customHeight="1">
+      <c r="B36" s="40" t="n">
+        <v>31</v>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>SYNA</t>
+        </is>
+      </c>
+      <c r="D36" s="40" t="inlineStr">
+        <is>
+          <t>Synaptics Incorporated</t>
+        </is>
+      </c>
+      <c r="E36" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42" t="inlineStr">
+        <is>
+          <t>Synaptics beat across the board (revenue $294.2m +10%, non-GAAP EPS $1.09) on a 31% jump in Core IoT - its sixth straight double-digit growth quarter - while flagging a possible 2H26 PC end-market slo</t>
+        </is>
+      </c>
+      <c r="I36" s="42" t="inlineStr">
+        <is>
+          <t>- Core IoT +31% YoY, sixth double-digit-growth quarter
+- FY26 Core IoT guide raised to &gt;40% growth
+- Edge AI/robotics design wins (35+ customers)</t>
+        </is>
+      </c>
+      <c r="J36" s="42" t="inlineStr">
+        <is>
+          <t>Management flagged possible 2H26 PC slowdown</t>
+        </is>
+      </c>
+      <c r="K36" s="42" t="inlineStr">
+        <is>
+          <t>127.5 (+4%)</t>
+        </is>
+      </c>
+      <c r="L36" s="42" t="inlineStr">
+        <is>
+          <t>211.9 (+73%)</t>
+        </is>
+      </c>
+      <c r="M36" s="42" t="inlineStr">
+        <is>
+          <t>- FQ4 2026 earnings
+- Core IoT / Edge AI design-win updates
+- PC end-market demand signals</t>
+        </is>
+      </c>
+      <c r="N36" s="42" t="inlineStr">
+        <is>
+          <t>Synaptics beat across the board (revenue $294.2M up 10%, non-GAAP EPS $1.09) on a 31% jump in Core IoT, its sixth straight double-digit growth quarter, while flagging a possible 2H26 PC end-market slowdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="B37" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>PRY.MI</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="E37" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G37" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="44" t="inlineStr">
+        <is>
+          <t>Prysmian is breaking out as the global HV cable backlog reaches record levels — grid build-out, offshore wind interconnects, and US transmission upgrades are all hitting simultaneously.</t>
+        </is>
+      </c>
+      <c r="I37" s="44" t="inlineStr">
+        <is>
+          <t>- EU €580B grid investment commitment through 2030
+- US IRA grid spending translating to cable orders
+- Data-center fiber + medium-voltage substation explosion</t>
+        </is>
+      </c>
+      <c r="J37" s="44" t="inlineStr">
+        <is>
+          <t>Copper price spikes compress margins with lag</t>
+        </is>
+      </c>
+      <c r="K37" s="44" t="inlineStr">
+        <is>
+          <t>144.5 (-1%)</t>
+        </is>
+      </c>
+      <c r="L37" s="44" t="inlineStr">
+        <is>
+          <t>208.3 (+43%)</t>
+        </is>
+      </c>
+      <c r="M37" s="44" t="inlineStr">
+        <is>
+          <t>- FY 2025 earnings (March 2026) — backlog + EBITDA guide
+- Encore Wire synergy update
+- Major HVDC tender awards H1 2026</t>
+        </is>
+      </c>
+      <c r="N37" s="44" t="inlineStr">
+        <is>
+          <t>Prysmian beat with Q1 revenue of 5.2B EUR (+9.4% YoY, +5.0% organic) and adj. EBITDA of 601M EUR (+14%, margin 14.2% / +110bps), with mgmt signaling they will exceed the top end of FY26 guidance on Transmission and Digital Solutions strengt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="96" customHeight="1">
+      <c r="B38" s="40" t="n">
+        <v>33</v>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="D38" s="40" t="inlineStr">
+        <is>
+          <t>GLOBALFOUNDRIES Inc.</t>
+        </is>
+      </c>
+      <c r="E38" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="42" t="inlineStr">
+        <is>
+          <t>GlobalFoundries beat on a record 29% gross margin (+510bps YoY) and EPS $0.40, guiding Q2 revenue up sequentially to ~$1.76bn as design wins surged 50% and customers prepaid for capacity in comms-infr</t>
+        </is>
+      </c>
+      <c r="I38" s="42" t="inlineStr">
+        <is>
+          <t>- Record 29% gross margin (+510bps YoY)
+- Design wins +50% with customer prepayments
+- Diversification: non-smart-mobile now 2/3 of revenue</t>
+        </is>
+      </c>
+      <c r="J38" s="42" t="inlineStr">
+        <is>
+          <t>Q2 GM guided down to 28.5% - record may be peak</t>
+        </is>
+      </c>
+      <c r="K38" s="42" t="inlineStr">
+        <is>
+          <t>110.5 (+46%)</t>
+        </is>
+      </c>
+      <c r="L38" s="42" t="inlineStr">
+        <is>
+          <t>206.7 (+174%)</t>
+        </is>
+      </c>
+      <c r="M38" s="42" t="inlineStr">
+        <is>
+          <t>- Q2 2026 earnings
+- Design-win and prepayment updates
+- Comms-infra / automotive demand trajectory</t>
+        </is>
+      </c>
+      <c r="N38" s="42" t="inlineStr">
+        <is>
+          <t>GlobalFoundries beat on a record 29% gross margin (+510bps YoY) and EPS $0.40, guiding Q2 revenue up sequentially to ~$1.76B as design wins surged 50% and customers prepaid for capacity in comms-infra and automotive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="96" customHeight="1">
+      <c r="B39" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>TWLO</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>Twilio Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G39" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="44" t="inlineStr">
+        <is>
+          <t>Twilio is breaking out as the AI-powered customer engagement platform thesis finally translates to revenue.</t>
+        </is>
+      </c>
+      <c r="I39" s="44" t="inlineStr">
+        <is>
+          <t>- AI-powered comms use cases driving wallet expansion
+- Operating margin expansion dropping to FCF
+- Capital allocation dramatically improved</t>
+        </is>
+      </c>
+      <c r="J39" s="44" t="inlineStr">
+        <is>
+          <t>CPaaS faces real pricing pressure (Bandwidth, Sinch)</t>
+        </is>
+      </c>
+      <c r="K39" s="44" t="inlineStr">
+        <is>
+          <t>177.2 (-22%)</t>
+        </is>
+      </c>
+      <c r="L39" s="44" t="inlineStr">
+        <is>
+          <t>286.4 (+27%)</t>
+        </is>
+      </c>
+      <c r="M39" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — net new ARR + margin commentary
+- Voice AI product launch updates
+- A2P pricing regulatory shifts</t>
+        </is>
+      </c>
+      <c r="N39" s="44" t="inlineStr">
+        <is>
+          <t>Twilio's fastest organic growth since 2022 (+16%) on voice AI inflection drove a sharp raise to FY26 guide and stock-based comp falling below 10% of revenue for the first time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="96" customHeight="1">
+      <c r="B40" s="40" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>SUBC.OL</t>
+        </is>
+      </c>
+      <c r="D40" s="40" t="inlineStr">
+        <is>
+          <t>Subsea 7 S.A.</t>
+        </is>
+      </c>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="42" t="inlineStr">
+        <is>
+          <t>Subsea 7 is breaking out as offshore oilfield services pricing finally turns and the company's record backlog (≈$10B+) translates into visible margin expansion through 2027.</t>
+        </is>
+      </c>
+      <c r="I40" s="42" t="inlineStr">
+        <is>
+          <t>- Record backlog ~$10B+ translates to margin expansion through 2027
+- OneSubsea JV winning disproportionate new field developments
+- Fleet utilization near 100% — pricing pass-through structural</t>
+        </is>
+      </c>
+      <c r="J40" s="42" t="inlineStr">
+        <is>
+          <t>Brent below $60 sustained freezes FID approvals</t>
+        </is>
+      </c>
+      <c r="K40" s="42" t="inlineStr">
+        <is>
+          <t>330.9 (+1%)</t>
+        </is>
+      </c>
+      <c r="L40" s="42" t="inlineStr">
+        <is>
+          <t>398.4 (+21%)</t>
+        </is>
+      </c>
+      <c r="M40" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — backlog quality + margin guide
+- Major Brazilian/Guyanese FID announcements
+- Petrobras 2026 capex plan</t>
+        </is>
+      </c>
+      <c r="N40" s="42" t="inlineStr">
+        <is>
+          <t>Q1 EBITDA +63% YoY drove a full-year guidance raise, with $13.5B backlog including $5B for 2027 cementing the multi-year offshore cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="96" customHeight="1">
+      <c r="B41" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>Rocket Lab Corporation</t>
+        </is>
+      </c>
+      <c r="E41" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G41" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="44" t="inlineStr">
+        <is>
+          <t>Rocket Lab posted record Q1 2026 revenue of $200.3m (+63.5% YoY, above guidance) on Launch and Space Systems strength, with Neutron on track for first launch later this year and a record-largest-ever</t>
+        </is>
+      </c>
+      <c r="I41" s="44" t="inlineStr">
+        <is>
+          <t>- Record Q1 revenue +63.5% YoY, above guidance
+- Neutron on track for first launch in 2026
+- Record booking velocity incl. largest-ever contract</t>
+        </is>
+      </c>
+      <c r="J41" s="44" t="inlineStr">
+        <is>
+          <t>Neutron schedule could slip to late 2026</t>
+        </is>
+      </c>
+      <c r="K41" s="44" t="inlineStr">
+        <is>
+          <t>105.3 (-4%)</t>
+        </is>
+      </c>
+      <c r="L41" s="44" t="inlineStr">
+        <is>
+          <t>150.0 (+36%)</t>
+        </is>
+      </c>
+      <c r="M41" s="44" t="inlineStr">
+        <is>
+          <t>- Neutron first launch / test milestones
+- Q2 2026 earnings
+- New launch + Space Systems contract awards</t>
+        </is>
+      </c>
+      <c r="N41" s="44" t="inlineStr">
+        <is>
+          <t>Rocket Lab posted record Q1 revenue of $200.3M (+63.5% YoY, above guidance) on Launch and Space Systems strength, with Neutron on track for first launch later this year and a record-largest-ever multi-launch customer contract booked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="96" customHeight="1">
+      <c r="B42" s="40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>NBIX</t>
+        </is>
+      </c>
+      <c r="D42" s="40" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences, Inc.</t>
+        </is>
+      </c>
+      <c r="E42" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences is breaking out as Crinecerfont (CAH program) and Ingrezza both meaningfully beat consensus on script volumes, and the pipeline credit (M1 muscarinic, schizophrenia program) is</t>
+        </is>
+      </c>
+      <c r="I42" s="42" t="inlineStr">
+        <is>
+          <t>- Crinecerfont + Ingrezza beat consensus on script volumes
+- Pipeline credit being re-rated after positive Phase 2
+- Ingrezza TD market much larger than initially modeled</t>
+        </is>
+      </c>
+      <c r="J42" s="42" t="inlineStr">
+        <is>
+          <t>Ingrezza patent cliff mid-2030s — pipeline must deliver</t>
+        </is>
+      </c>
+      <c r="K42" s="42" t="inlineStr">
+        <is>
+          <t>167.3 (+2%)</t>
+        </is>
+      </c>
+      <c r="L42" s="42" t="inlineStr">
+        <is>
+          <t>226.2 (+38%)</t>
+        </is>
+      </c>
+      <c r="M42" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — Crinecerfont launch metrics
+- Phase 3 muscarinic program data H1 2026
+- CMS pricing decision cycle</t>
+        </is>
+      </c>
+      <c r="N42" s="42" t="inlineStr">
+        <is>
+          <t>First-ever $800M+ revenue quarter (+44% YoY) with CRENESSITY launch running ahead of plan and now annualizing above $600M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="96" customHeight="1">
+      <c r="B43" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>Corcept Therapeutics Incorpora</t>
+        </is>
+      </c>
+      <c r="E43" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G43" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="44" t="inlineStr">
+        <is>
+          <t>Corcept raised FY2026 revenue guidance to $950m-$1.05bn as Lifyorli won early FDA approval in platinum-resistant ovarian cancer (3.5 months ahead of PDUFA) and the Cushing's franchise marches toward a</t>
+        </is>
+      </c>
+      <c r="I43" s="44" t="inlineStr">
+        <is>
+          <t>- FY26 revenue guidance raised to $950m-$1.05bn
+- Lifyorli approved early in platinum-resistant ovarian cancer
+- ROSELLA met PFS and overall-survival endpoints</t>
+        </is>
+      </c>
+      <c r="J43" s="44" t="inlineStr">
+        <is>
+          <t>Ovarian TAM is a 35-40% patient subset</t>
+        </is>
+      </c>
+      <c r="K43" s="44" t="inlineStr">
+        <is>
+          <t>64.2 (-12%)</t>
+        </is>
+      </c>
+      <c r="L43" s="44" t="inlineStr">
+        <is>
+          <t>94.5 (+30%)</t>
+        </is>
+      </c>
+      <c r="M43" s="44" t="inlineStr">
+        <is>
+          <t>- Lifyorli launch uptake / scripts
+- Relacorilant Cushing's FDA decision
+- Q2 2026 earnings</t>
+        </is>
+      </c>
+      <c r="N43" s="44" t="inlineStr">
+        <is>
+          <t>Corcept raised FY2026 revenue guidance to $950M-$1.05B as Lifyorli (relacorilant) won early FDA approval in platinum-resistant ovarian cancer (3.5 months ahead of PDUFA) and the Cushing's franchise marches toward a $2B+ target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="96" customHeight="1">
+      <c r="B44" s="40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>HUM</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="inlineStr">
+        <is>
+          <t>Humana Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="42" t="inlineStr">
+        <is>
+          <t>Humana is breaking out as the worst of the Medicare Advantage margin reset (driven by 2024 utilization spike) appears to be behind the company.</t>
+        </is>
+      </c>
+      <c r="I44" s="42" t="inlineStr">
+        <is>
+          <t>- MA enrollment growing structurally as boomers age in
+- One of two scaled pure-play MA insurers
+- 2027 bid season looks more rational</t>
+        </is>
+      </c>
+      <c r="J44" s="42" t="inlineStr">
+        <is>
+          <t>CMS reimbursement + risk adjustment political</t>
+        </is>
+      </c>
+      <c r="K44" s="42" t="inlineStr">
+        <is>
+          <t>306.3 (-13%)</t>
+        </is>
+      </c>
+      <c r="L44" s="42" t="inlineStr">
+        <is>
+          <t>438.1 (+25%)</t>
+        </is>
+      </c>
+      <c r="M44" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — 2026 guidance + MLR commentary
+- 2027 CMS Advance Notice (April 2026)
+- Star ratings September 2026</t>
+        </is>
+      </c>
+      <c r="N44" s="42" t="inlineStr">
+        <is>
+          <t>Humana delivered Q1 adjusted EPS of $10.31 at the high end of guide with Insurance benefit ratio of 89.4% favorable to the 'just under 90%' target, affirming FY26 guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="96" customHeight="1">
+      <c r="B45" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>MELE.BR</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>Melexis NV</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G45" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="44" t="inlineStr">
+        <is>
+          <t>Melexis Q1 sales of EUR202.1M came in soft with a 4ppt FX headwind, but mgmt held the FY26 EUR830-880M sales guide implying a stronger H2 ramp as Tier-1 inventories normalize and new EV/HEV design win</t>
+        </is>
+      </c>
+      <c r="I45" s="44" t="inlineStr">
+        <is>
+          <t>- EV/HEV content-per-vehicle continues stepping up
+- Asian OEM design wins underpin H2 ramp
+- Inventory normalization at Tier-1s is genuine</t>
+        </is>
+      </c>
+      <c r="J45" s="44" t="inlineStr">
+        <is>
+          <t>H2 ramp is execution-risk; guide carries hair</t>
+        </is>
+      </c>
+      <c r="K45" s="44" t="inlineStr">
+        <is>
+          <t>130.5 (+62%)</t>
+        </is>
+      </c>
+      <c r="L45" s="44" t="inlineStr">
+        <is>
+          <t>237.6 (+195%)</t>
+        </is>
+      </c>
+      <c r="M45" s="44" t="inlineStr">
+        <is>
+          <t>- H1 print (late July)
+- Tier-1 restock data
+- China EV monthly volumes</t>
+        </is>
+      </c>
+      <c r="N45" s="44" t="inlineStr">
+        <is>
+          <t>Melexis Q1 sales of EUR202.1M came in soft with a 4ppt FX headwind from a weaker dollar and gross margin compressed to 39.9%, with management flagging a still-muted automotive semis recovery into H2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="B46" s="40" t="n">
+        <v>41</v>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>MTSI</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>MACOM Technology Solutions Hol</t>
+        </is>
+      </c>
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="42" t="inlineStr">
+        <is>
+          <t>MACOM is breaking out as defense radar and high-speed datacom orders both accelerate.</t>
+        </is>
+      </c>
+      <c r="I46" s="42" t="inlineStr">
+        <is>
+          <t>- Defense radar + high-speed datacom orders accelerating
+- Wolfspeed RF acquisition meaningfully accretive
+- Convergence of defense modernization + AI datacom</t>
+        </is>
+      </c>
+      <c r="J46" s="42" t="inlineStr">
+        <is>
+          <t>Wolfspeed RF integration cost early innings</t>
+        </is>
+      </c>
+      <c r="K46" s="42" t="inlineStr">
+        <is>
+          <t>242.3 (-30%)</t>
+        </is>
+      </c>
+      <c r="L46" s="42" t="inlineStr">
+        <is>
+          <t>353.9 (+2%)</t>
+        </is>
+      </c>
+      <c r="M46" s="42" t="inlineStr">
+        <is>
+          <t>- Q1 FY26 earnings (Feb 2026) — Wolfspeed integration update
+- FY27 defense budget
+- Major hyperscaler optical RFP awards</t>
+        </is>
+      </c>
+      <c r="N46" s="42" t="inlineStr">
+        <is>
+          <t>Data Center inflection drives Q3 guide to $335M (Street $300M) and full-year DC growth raised to 35-40% on 1.6T optical ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="96" customHeight="1">
+      <c r="B47" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>UMI.BR</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>Umicore SA</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G47" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="44" t="inlineStr">
+        <is>
+          <t>Umicore raised FY26 EBITDA guidance to ~EUR1.0B and lowered leverage outlook to &lt;2x on stronger metal prices and Catalysis outperformance versus the global light-duty vehicle market.</t>
+        </is>
+      </c>
+      <c r="I47" s="44" t="inlineStr">
+        <is>
+          <t>- FY26 EBITDA guide raised to ~EUR1.0B
+- Net leverage path to &lt;2x supports buyback optionality
+- Recycling running near record on PGM mix</t>
+        </is>
+      </c>
+      <c r="J47" s="44" t="inlineStr">
+        <is>
+          <t>Metal-price tailwind reversal</t>
+        </is>
+      </c>
+      <c r="K47" s="44" t="inlineStr">
+        <is>
+          <t>33.7 (+44%)</t>
+        </is>
+      </c>
+      <c r="L47" s="44" t="inlineStr">
+        <is>
+          <t>44.2 (+89%)</t>
+        </is>
+      </c>
+      <c r="M47" s="44" t="inlineStr">
+        <is>
+          <t>- H1 2026 results (July)
+- Battery Materials strategic update
+- PGM market moves</t>
+        </is>
+      </c>
+      <c r="N47" s="44" t="inlineStr">
+        <is>
+          <t>Umicore raised FY26 EBITDA guidance to ~EUR1.0B and lowered leverage outlook to &lt;2x on the back of stronger metal prices and Catalysis outperformance vs the global light-duty vehicle market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="96" customHeight="1">
+      <c r="B48" s="40" t="n">
+        <v>43</v>
+      </c>
+      <c r="C48" s="40" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="D48" s="40" t="inlineStr">
+        <is>
+          <t>Lumentum Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="42" t="inlineStr">
+        <is>
+          <t>Lumentum is breaking out as datacom transceiver demand and the new EML laser business ramp at hyperscaler customers.</t>
+        </is>
+      </c>
+      <c r="I48" s="42" t="inlineStr">
+        <is>
+          <t>- EML laser ramp at hyperscaler customers
+- Cloud Light integration better than guided
+- 3D-sensing iPhone business stabilizing</t>
+        </is>
+      </c>
+      <c r="J48" s="42" t="inlineStr">
+        <is>
+          <t>Heavy NVIDIA concentration</t>
+        </is>
+      </c>
+      <c r="K48" s="42" t="inlineStr">
+        <is>
+          <t>816.2 (-5%)</t>
+        </is>
+      </c>
+      <c r="L48" s="42" t="inlineStr">
+        <is>
+          <t>1116.7 (+29%)</t>
+        </is>
+      </c>
+      <c r="M48" s="42" t="inlineStr">
+        <is>
+          <t>- Q2 FY26 earnings (Feb 2026) — Cloud Light + Apple commentary
+- NVIDIA networking attach rate updates
+- Apple iPhone 18 supply ramp</t>
+        </is>
+      </c>
+      <c r="N48" s="42" t="inlineStr">
+        <is>
+          <t>NVIDIA $2B direct investment plus record $808M revenue (+90% YoY) reframes Lumentum as a strategic AI optics supplier with structural supply tightness through CY26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="96" customHeight="1">
+      <c r="B49" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="C49" s="43" t="inlineStr">
+        <is>
+          <t>ATT.L</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
+        <is>
+          <t>Allianz Technology Trust PLC</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G49" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="44" t="inlineStr">
+        <is>
+          <t>ATT.L is breaking out with the AI/tech equity rally; FY2025 results (March 2026) showed a NAV total return of +24.7% vs benchmark +20.0%.</t>
+        </is>
+      </c>
+      <c r="I49" s="44" t="inlineStr">
+        <is>
+          <t>- FY25 NAV total return +24.7% vs +20.0% benchmark
+- Concentrated US AI/tech exposure
+- Discount-to-NAV narrowing adds return</t>
+        </is>
+      </c>
+      <c r="J49" s="44" t="inlineStr">
+        <is>
+          <t>No moat - pure tech beta</t>
+        </is>
+      </c>
+      <c r="K49" s="44" t="inlineStr"/>
+      <c r="L49" s="44" t="inlineStr"/>
+      <c r="M49" s="44" t="inlineStr">
+        <is>
+          <t>- NAV updates / interim results
+- Nasdaq/semis direction
+- Discount-management actions</t>
+        </is>
+      </c>
+      <c r="N49" s="44" t="inlineStr">
+        <is>
+          <t>Vehicle does not issue quarterly earnings - Allianz Technology Trust is a closed-end investment trust; FY2025 final results (announced March 17, 2026) reported NAV total return +24.7% vs benchmark +20.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="96" customHeight="1">
+      <c r="B50" s="40" t="n">
+        <v>45</v>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>MNTN.L</t>
+        </is>
+      </c>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>The Schiehallion Fund Limited</t>
+        </is>
+      </c>
+      <c r="E50" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="42" t="inlineStr">
+        <is>
+          <t>Schiehallion Fund (the Baillie Gifford private-tech vehicle) is breaking out as portfolio mark-ups on private holdings catch up to public market re-rating.</t>
+        </is>
+      </c>
+      <c r="I50" s="42" t="inlineStr">
+        <is>
+          <t>- Portfolio mark-ups catching public market re-rating
+- NAV discount narrowing as confidence returns
+- Baillie Gifford concentration paying off</t>
+        </is>
+      </c>
+      <c r="J50" s="42" t="inlineStr">
+        <is>
+          <t>NAV opaque — private mark subjectivity</t>
+        </is>
+      </c>
+      <c r="K50" s="42" t="inlineStr">
+        <is>
+          <t>1.8 (-20%)</t>
+        </is>
+      </c>
+      <c r="L50" s="42" t="inlineStr">
+        <is>
+          <t>1.9 (-11%)</t>
+        </is>
+      </c>
+      <c r="M50" s="42" t="inlineStr">
+        <is>
+          <t>- Interim NAV updates monthly
+- SpaceX/Stripe/Bytedance secondary pricing
+- Major private holding IPO timing</t>
+        </is>
+      </c>
+      <c r="N50" s="42" t="inlineStr">
+        <is>
+          <t>Vehicle does not issue quarterly earnings - Baillie Gifford-managed late-stage private growth trust reports semi-annual NAV with monthly factsheet updates; shares trade at ~4% premium to NAV after a 120% 12-month rally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="96" customHeight="1">
+      <c r="B51" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="C51" s="43" t="inlineStr">
+        <is>
+          <t>SNX</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>TD SYNNEX Corporation</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G51" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="44" t="inlineStr">
+        <is>
+          <t>TD Synnex is breaking out as the IT distribution cycle normalizes and AI-related infrastructure refresh accelerates.</t>
+        </is>
+      </c>
+      <c r="I51" s="44" t="inlineStr">
+        <is>
+          <t>- IT distribution cycle normalizing
+- AI infrastructure refresh accelerating
+- Tech Data merger synergies above guidance</t>
+        </is>
+      </c>
+      <c r="J51" s="44" t="inlineStr">
+        <is>
+          <t>Same distribution-margin risk as Arrow</t>
+        </is>
+      </c>
+      <c r="K51" s="44" t="inlineStr">
+        <is>
+          <t>425.7 (+58%)</t>
+        </is>
+      </c>
+      <c r="L51" s="44" t="inlineStr">
+        <is>
+          <t>621.7 (+131%)</t>
+        </is>
+      </c>
+      <c r="M51" s="44" t="inlineStr">
+        <is>
+          <t>- Q1 FY26 earnings (Jan 2026) — billings + AI server segment
+- Major hyperscaler partnership announcements
+- Tech Data integration milestones</t>
+        </is>
+      </c>
+      <c r="N51" s="44" t="inlineStr">
+        <is>
+          <t>TD SYNNEX crushed Q1 with EPS of $4.73 vs $3.32 consensus on 24% non-GAAP gross billings growth, led by a 95% surge in Hive driven by AI/cloud data center demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="96" customHeight="1">
+      <c r="B52" s="40" t="n">
+        <v>47</v>
+      </c>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>CCC.L</t>
+        </is>
+      </c>
+      <c r="D52" s="40" t="inlineStr">
+        <is>
+          <t>Computacenter plc</t>
+        </is>
+      </c>
+      <c r="E52" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G52" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="42" t="inlineStr">
+        <is>
+          <t>Computacenter broke 9bn pounds revenue (+32% to 9.2bn) on a near-doubling of North America profit and a record 7.1bn-pound product order backlog (+200% cc), even as pre-tax profit slipped 2.5% to 238.</t>
+        </is>
+      </c>
+      <c r="I52" s="42" t="inlineStr">
+        <is>
+          <t>- Revenue broke 9bn (+32%) on NA strength
+- Record 7.1bn product backlog (+200% cc)
+- North America profit nearly doubled, now ~40% of group</t>
+        </is>
+      </c>
+      <c r="J52" s="42" t="inlineStr">
+        <is>
+          <t>Hardware-heavy mix pressured margins (PBT -2.5%)</t>
+        </is>
+      </c>
+      <c r="K52" s="42" t="inlineStr">
+        <is>
+          <t>5352.4 (+23%)</t>
+        </is>
+      </c>
+      <c r="L52" s="42" t="inlineStr">
+        <is>
+          <t>7570.1 (+74%)</t>
+        </is>
+      </c>
+      <c r="M52" s="42" t="inlineStr">
+        <is>
+          <t>- H1 FY26 results
+- Backlog conversion / NA hyperscale demand
+- Services-mix and margin recovery</t>
+        </is>
+      </c>
+      <c r="N52" s="42" t="inlineStr">
+        <is>
+          <t>Computacenter broke 9bn pounds revenue (+32% to 9.2bn) on a near-doubling of North America profit and a record 7.1bn pound product order backlog (+200% cc), even as pre-tax profit slipped 2.5% to 238.5m on mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="96" customHeight="1">
+      <c r="B53" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="C53" s="43" t="inlineStr">
+        <is>
+          <t>SCT.L</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>Softcat plc</t>
+        </is>
+      </c>
+      <c r="E53" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F53" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G53" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="44" t="inlineStr">
+        <is>
+          <t>Softcat is breaking out as UK IT-reseller demand normalizes post-2024 weakness and AI-related infrastructure refresh accelerates.</t>
+        </is>
+      </c>
+      <c r="I53" s="44" t="inlineStr">
+        <is>
+          <t>- UK IT-reseller demand normalizing
+- AI-related hardware refresh accelerating
+- Best-in-class customer service moat</t>
+        </is>
+      </c>
+      <c r="J53" s="44" t="inlineStr">
+        <is>
+          <t>UK SMB IT spending sensitive to UK macro</t>
+        </is>
+      </c>
+      <c r="K53" s="44" t="inlineStr">
+        <is>
+          <t>2193.1 (+17%)</t>
+        </is>
+      </c>
+      <c r="L53" s="44" t="inlineStr">
+        <is>
+          <t>3116.8 (+66%)</t>
+        </is>
+      </c>
+      <c r="M53" s="44" t="inlineStr">
+        <is>
+          <t>- H1 trading update (Jan 2026) — gross profit growth
+- UK macro inflection signals
+- Microsoft/Cisco channel partner programs</t>
+        </is>
+      </c>
+      <c r="N53" s="44" t="inlineStr">
+        <is>
+          <t>Softcat's H1 FY26 came in 'significantly ahead' of plan on an AI-datacentre hardware surge (GII +33% to 2bn, op profit +27%), prompting CEO Charlton to declare a 'golden era' and raise the FY26 op-profit guide twice in nine weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="96" customHeight="1">
+      <c r="B54" s="40" t="n">
+        <v>49</v>
+      </c>
+      <c r="C54" s="40" t="inlineStr">
+        <is>
+          <t>ARW</t>
+        </is>
+      </c>
+      <c r="D54" s="40" t="inlineStr">
+        <is>
+          <t>Arrow Electronics, Inc.</t>
+        </is>
+      </c>
+      <c r="E54" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="42" t="inlineStr">
+        <is>
+          <t>Arrow Electronics is breaking out as electronic components distribution stabilizes after a brutal 2024 destocking cycle.</t>
+        </is>
+      </c>
+      <c r="I54" s="42" t="inlineStr">
+        <is>
+          <t>- Distribution stabilizes after 2024 destocking
+- ECS segment grows with cloud commitments
+- Counter-cyclical mix balance</t>
+        </is>
+      </c>
+      <c r="J54" s="42" t="inlineStr">
+        <is>
+          <t>Distribution structurally low-margin</t>
+        </is>
+      </c>
+      <c r="K54" s="42" t="inlineStr">
+        <is>
+          <t>219.5 (+0%)</t>
+        </is>
+      </c>
+      <c r="L54" s="42" t="inlineStr">
+        <is>
+          <t>260.0 (+19%)</t>
+        </is>
+      </c>
+      <c r="M54" s="42" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — segment normalization
+- Semi book-to-bill ratios
+- Major hyperscaler distribution agreements</t>
+        </is>
+      </c>
+      <c r="N54" s="42" t="inlineStr">
+        <is>
+          <t>Arrow Electronics blew the doors off with EPS of $5.22 vs $2.82 consensus and revenue +39% YoY to $9.5B, signaling a sharper-than-expected components cycle inflection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="96" customHeight="1">
+      <c r="B55" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
+        <is>
+          <t>AMKR</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="inlineStr">
+        <is>
+          <t>Amkor Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E55" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" s="43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G55" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="44" t="inlineStr">
+        <is>
+          <t>Amkor is breaking out as advanced packaging demand for AI accelerators ramps and the company's Vietnam facility comes online.</t>
+        </is>
+      </c>
+      <c r="I55" s="44" t="inlineStr">
+        <is>
+          <t>- Advanced packaging fastest-growing semis segment
+- TSMC CoWoS bottleneck pushes business to OSATs
+- Vietnam facility online</t>
+        </is>
+      </c>
+      <c r="J55" s="44" t="inlineStr">
+        <is>
+          <t>Customer concentration (Apple ~25%, hyperscalers)</t>
+        </is>
+      </c>
+      <c r="K55" s="44" t="inlineStr">
+        <is>
+          <t>75.8 (+17%)</t>
+        </is>
+      </c>
+      <c r="L55" s="44" t="inlineStr">
+        <is>
+          <t>105.3 (+62%)</t>
+        </is>
+      </c>
+      <c r="M55" s="44" t="inlineStr">
+        <is>
+          <t>- Q4 2025 earnings (Feb 2026) — advanced packaging revenue mix
+- TSMC CoWoS expansion announcements
+- Apple iPhone 17 production ramp</t>
+        </is>
+      </c>
+      <c r="N55" s="44" t="inlineStr">
+        <is>
+          <t>Record Q1 with 27% YoY revenue growth as advanced packaging for AI tripled in 2026 outlook and iOS/HBM ramps drove a strong Q2 guide.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -12222,11 +15702,15 @@
           <t>RPI.L</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12266,7 +15750,7 @@
       <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -12282,10 +15766,10 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="36" t="inlineStr">
         <is>
@@ -12302,11 +15786,15 @@
           <t>ARM</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12319,11 +15807,15 @@
           <t>MRVL</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12337,12 +15829,12 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -12358,10 +15850,10 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="36" t="inlineStr">
         <is>
@@ -12378,11 +15870,15 @@
           <t>IFX.DE</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12395,11 +15891,15 @@
           <t>ALAB</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D15" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12413,12 +15913,12 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -12433,11 +15933,15 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D17" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12451,12 +15955,12 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F18" s="37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -12472,14 +15976,14 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="38" t="inlineStr">
-        <is>
-          <t>RISING</t>
+        <v>0</v>
+      </c>
+      <c r="F19" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12493,14 +15997,14 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>-9</v>
-      </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12535,12 +16039,12 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F22" s="37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -12556,14 +16060,14 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="F23" s="40" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F23" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12577,14 +16081,14 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F24" s="35" t="inlineStr">
         <is>
-          <t>RISING</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12597,11 +16101,15 @@
           <t>TEM.L</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D25" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12615,12 +16123,12 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F26" s="37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -12635,11 +16143,15 @@
           <t>OGN</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D27" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12652,11 +16164,15 @@
           <t>SITM</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F28" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12670,14 +16186,14 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>-16</v>
-      </c>
-      <c r="F29" s="40" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F29" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12691,14 +16207,14 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>-12</v>
-      </c>
-      <c r="F30" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12711,11 +16227,15 @@
           <t>AFRM</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D31" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12728,11 +16248,15 @@
           <t>IRDM</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
+      <c r="D32" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F32" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12746,14 +16270,14 @@
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>-13</v>
-      </c>
-      <c r="F33" s="40" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F33" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12767,14 +16291,14 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>-25</v>
-      </c>
-      <c r="F34" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F34" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12787,11 +16311,15 @@
           <t>PCT.L</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D35" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12804,11 +16332,15 @@
           <t>SYNA</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12822,14 +16354,14 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>-22</v>
-      </c>
-      <c r="F37" s="40" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F37" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12842,11 +16374,15 @@
           <t>GFS</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr"/>
+      <c r="D38" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12860,10 +16396,10 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="36" t="inlineStr">
         <is>
@@ -12881,14 +16417,14 @@
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>-18</v>
-      </c>
-      <c r="F40" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12901,11 +16437,15 @@
           <t>RKLB</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr"/>
-      <c r="F41" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D41" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12919,14 +16459,14 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-12</v>
-      </c>
-      <c r="F42" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12939,11 +16479,15 @@
           <t>CORT</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D43" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12957,14 +16501,14 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>RISING</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12977,11 +16521,15 @@
           <t>MELE.BR</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr"/>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D45" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -12995,14 +16543,14 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>-15</v>
-      </c>
-      <c r="F46" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13015,11 +16563,15 @@
           <t>UMI.BR</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr"/>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D47" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13033,14 +16585,14 @@
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-21</v>
-      </c>
-      <c r="F48" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F48" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13053,11 +16605,15 @@
           <t>ATT.L</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr"/>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="38" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="D49" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13071,14 +16627,14 @@
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>-11</v>
-      </c>
-      <c r="F50" s="39" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F50" s="35" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13092,10 +16648,10 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F51" s="36" t="inlineStr">
         <is>
@@ -13112,11 +16668,15 @@
           <t>CCC.L</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr"/>
+      <c r="D52" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13130,14 +16690,14 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="F53" s="40" t="inlineStr">
-        <is>
-          <t>FALLING</t>
+        <v>0</v>
+      </c>
+      <c r="F53" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -13151,12 +16711,12 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F54" s="37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
         <is>
           <t>STABLE</t>
         </is>
@@ -13172,354 +16732,14 @@
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>-19</v>
-      </c>
-      <c r="F55" s="40" t="inlineStr">
-        <is>
-          <t>FALLING</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="8" t="inlineStr"/>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>AJB.L</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="E56" s="8" t="inlineStr"/>
-      <c r="F56" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>AKAM</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="8" t="inlineStr"/>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>AKRBP.OL</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="9" t="inlineStr"/>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>ASM.AS</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="8" t="inlineStr"/>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>BP.L</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="9" t="inlineStr"/>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>BWLPG.OL</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="8" t="inlineStr"/>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>DPLM.L</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="8" t="inlineStr"/>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>EQNR.OL</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="E64" s="8" t="inlineStr"/>
-      <c r="F64" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="9" t="inlineStr"/>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="8" t="inlineStr"/>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="9" t="inlineStr"/>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>GLW</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="8" t="inlineStr"/>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>IGG.L</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="9" t="inlineStr"/>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>LSCC</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="E69" s="9" t="inlineStr"/>
-      <c r="F69" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="8" t="inlineStr"/>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>MTZ</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="9" t="inlineStr"/>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>NHY.OL</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="E71" s="9" t="inlineStr"/>
-      <c r="F71" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="8" t="inlineStr"/>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>SPM.MI</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="9" t="inlineStr"/>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>TCAP.L</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="E73" s="9" t="inlineStr"/>
-      <c r="F73" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr"/>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>TGS.OL</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="E74" s="8" t="inlineStr"/>
-      <c r="F74" s="41" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="9" t="inlineStr"/>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>VAR.OL</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="E75" s="9" t="inlineStr"/>
-      <c r="F75" s="42" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
+        <v>0</v>
+      </c>
+      <c r="F55" s="36" t="inlineStr">
+        <is>
+          <t>STABLE</t>
         </is>
       </c>
     </row>
@@ -33026,18 +36246,10 @@
       <c r="E30" s="8" t="n">
         <v>325</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v/>
-      </c>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -33376,18 +36588,10 @@
       <c r="E40" s="8" t="n">
         <v>684</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v/>
-      </c>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
       <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -33866,18 +37070,10 @@
       <c r="E54" s="8" t="n">
         <v>721</v>
       </c>
-      <c r="F54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="G54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="H54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v/>
-      </c>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
